--- a/spravki/spravka_rnntd_industry_2026-09-30.xlsx
+++ b/spravki/spravka_rnntd_industry_2026-09-30.xlsx
@@ -512,16 +512,16 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>148</v>
+        <v>161</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>66.2</t>
+          <t>44.1</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>21.6</t>
+          <t>21.9</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -531,54 +531,54 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>5.1</t>
+          <t>5.3</t>
         </is>
       </c>
       <c r="G6" t="n">
-        <v>859</v>
+        <v>938</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Здравоохранение</t>
+          <t>Не указано</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>42</v>
+        <v>61</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>10.5</t>
+          <t>7.2</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>12.2</t>
+          <t>0.1</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>2.0</t>
+          <t>0.1</t>
         </is>
       </c>
       <c r="G7" t="n">
-        <v>267</v>
+        <v>78</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Обрабатывающая промышленность</t>
+          <t>Здравоохранение</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>34</v>
+        <v>42</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -587,40 +587,40 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2.7</t>
+          <t>12.2</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0.2</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>0.9</t>
+          <t>2.0</t>
         </is>
       </c>
       <c r="G8" t="n">
-        <v>218</v>
+        <v>267</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Не указано</t>
+          <t>Обрабатывающая промышленность</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>31</v>
+        <v>38</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>8.1</t>
+          <t>11.7</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>0.9</t>
+          <t>3.1</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -630,11 +630,11 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>0.3</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="G9" t="n">
-        <v>91</v>
+        <v>231</v>
       </c>
     </row>
     <row r="10">
@@ -644,11 +644,11 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>8.0</t>
+          <t>8.6</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -677,11 +677,11 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>7.9</t>
+          <t>8.8</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -710,11 +710,11 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>5.6</t>
+          <t>6.2</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -743,16 +743,16 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>4.1</t>
+          <t>4.6</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>1.2</t>
+          <t>1.3</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -772,20 +772,20 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Качественное образование</t>
+          <t>Геология, добыча и переработка полезных ископаемых, новые материалы и технологии</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>2.9</t>
+          <t>3.3</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>0.5</t>
+          <t>1.3</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -799,17 +799,17 @@
         </is>
       </c>
       <c r="G14" t="n">
-        <v>74</v>
+        <v>72</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Геология, добыча и переработка полезных ископаемых, новые материалы и технологии</t>
+          <t>Качественное образование</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -818,7 +818,7 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>0.9</t>
+          <t>0.5</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -828,30 +828,30 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>0.3</t>
         </is>
       </c>
       <c r="G15" t="n">
-        <v>67</v>
+        <v>74</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Модернизация энергетического комплекса</t>
+          <t>Металлургия и металлообработка</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>1.1</t>
+          <t>2.1</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>1.1</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -865,26 +865,26 @@
         </is>
       </c>
       <c r="G16" t="n">
-        <v>71</v>
+        <v>31</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Иные сектора экономики</t>
+          <t>Модернизация энергетического комплекса</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>2.0</t>
+          <t>2.1</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>1.2</t>
+          <t>1.4</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -894,30 +894,30 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>0.1</t>
+          <t>0.3</t>
         </is>
       </c>
       <c r="G17" t="n">
-        <v>31</v>
+        <v>74</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Металлургия и металлообработка</t>
+          <t>Иные сектора экономики</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>1.1</t>
+          <t>1.9</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>1.2</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -927,7 +927,7 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>0.3</t>
+          <t>0.1</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -1073,16 +1073,16 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>0.6</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>0.5</t>
+          <t>0.6</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -1096,13 +1096,13 @@
         </is>
       </c>
       <c r="G23" t="n">
-        <v>5</v>
+        <v>11</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Источник: «Показатели проектов на 30.09.2026», проектов в выборке — 407. Сформировано 16.10.2026.</t>
+          <t>Источник: «Показатели проектов на 30.09.2026», проектов в выборке — 475. Сформировано 16.10.2026.</t>
         </is>
       </c>
     </row>
